--- a/research/traditional_assets/database/data/chile/chile_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_financial_svcs_non_bank_insurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0441</v>
+        <v>0.12475</v>
       </c>
       <c r="E2">
-        <v>0.048</v>
+        <v>0.11085</v>
       </c>
       <c r="G2">
-        <v>0.1400521065006037</v>
+        <v>0.1493160927123191</v>
       </c>
       <c r="H2">
-        <v>0.1318548643324649</v>
+        <v>0.1432906715925584</v>
       </c>
       <c r="I2">
-        <v>0.2012398524487941</v>
+        <v>0.1052444102301238</v>
       </c>
       <c r="J2">
-        <v>0.1537004346465864</v>
+        <v>0.09627914565496511</v>
       </c>
       <c r="K2">
-        <v>241.75</v>
+        <v>242.6</v>
       </c>
       <c r="L2">
-        <v>0.153618860011438</v>
+        <v>0.1066983331134275</v>
       </c>
       <c r="M2">
-        <v>142.92</v>
+        <v>64.27579999999999</v>
       </c>
       <c r="N2">
-        <v>0.1198490566037736</v>
+        <v>0.04729639440765268</v>
       </c>
       <c r="O2">
-        <v>0.5911892450879007</v>
+        <v>0.2649455894476504</v>
       </c>
       <c r="P2">
-        <v>142.92</v>
+        <v>64.27579999999999</v>
       </c>
       <c r="Q2">
-        <v>0.1198490566037736</v>
+        <v>0.04729639440765268</v>
       </c>
       <c r="R2">
-        <v>0.5911892450879007</v>
+        <v>0.2649455894476504</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +636,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2008.71</v>
+        <v>1180.63</v>
       </c>
       <c r="V2">
-        <v>1.684452830188679</v>
+        <v>0.8687490802060338</v>
       </c>
       <c r="W2">
-        <v>0.1840195922229473</v>
+        <v>0.2064499350853567</v>
       </c>
       <c r="X2">
-        <v>0.03908002231899779</v>
+        <v>0.06809995409231617</v>
       </c>
       <c r="Y2">
-        <v>0.1449395699039495</v>
+        <v>0.1383499809930405</v>
       </c>
       <c r="Z2">
-        <v>0.3971974602320981</v>
+        <v>0.5461227238724513</v>
       </c>
       <c r="AA2">
-        <v>0.1386063455286567</v>
+        <v>0.1488557938972117</v>
       </c>
       <c r="AB2">
-        <v>0.02586808636262147</v>
+        <v>0.05050711978851457</v>
       </c>
       <c r="AC2">
-        <v>0.1127382591660352</v>
+        <v>0.09834867410869719</v>
       </c>
       <c r="AD2">
-        <v>4807.601000000001</v>
+        <v>5234.001</v>
       </c>
       <c r="AE2">
-        <v>0.07922100666345055</v>
+        <v>0.05892229883763454</v>
       </c>
       <c r="AF2">
-        <v>4807.680221006664</v>
+        <v>5234.059922298838</v>
       </c>
       <c r="AG2">
-        <v>2798.970221006664</v>
+        <v>4053.429922298837</v>
       </c>
       <c r="AH2">
-        <v>0.8012559696415367</v>
+        <v>0.7938741622226679</v>
       </c>
       <c r="AI2">
-        <v>0.7721965136968137</v>
+        <v>0.7948627585188748</v>
       </c>
       <c r="AJ2">
-        <v>0.7012379063423786</v>
+        <v>0.7489112987124297</v>
       </c>
       <c r="AK2">
-        <v>0.6636924063022333</v>
+        <v>0.750047644267252</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.003</v>
+        <v>-0.188</v>
       </c>
       <c r="AN2">
-        <v>14.86088709054209</v>
+        <v>21.31055837398109</v>
       </c>
       <c r="AP2">
-        <v>8.651961846286678</v>
+        <v>16.50379030764248</v>
       </c>
       <c r="AQ2">
-        <v>-105566.6666666667</v>
+        <v>-1272.872340425532</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0385</v>
+        <v>0.0605</v>
       </c>
       <c r="E3">
-        <v>-0.064</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="G3">
-        <v>0.4012345679012346</v>
+        <v>0.41</v>
       </c>
       <c r="H3">
-        <v>0.4012345679012346</v>
+        <v>0.41</v>
       </c>
       <c r="I3">
-        <v>0.3703703703703704</v>
+        <v>0.37</v>
       </c>
       <c r="J3">
-        <v>0.2751760024487298</v>
+        <v>0.3069629629629629</v>
       </c>
       <c r="K3">
-        <v>8.949999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="L3">
-        <v>0.2762345679012346</v>
+        <v>0.37</v>
       </c>
       <c r="M3">
-        <v>7.92</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="N3">
-        <v>0.08</v>
+        <v>0.08346774193548387</v>
       </c>
       <c r="O3">
-        <v>0.8849162011173185</v>
+        <v>0.7459459459459459</v>
       </c>
       <c r="P3">
-        <v>7.92</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.08</v>
+        <v>0.08346774193548387</v>
       </c>
       <c r="R3">
-        <v>0.8849162011173185</v>
+        <v>0.7459459459459459</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,70 +767,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>8.41</v>
+        <v>7.83</v>
       </c>
       <c r="V3">
-        <v>0.08494949494949496</v>
+        <v>0.07893145161290323</v>
       </c>
       <c r="W3">
-        <v>0.1916488222698073</v>
+        <v>0.2407809110629067</v>
       </c>
       <c r="X3">
-        <v>0.02432309625867765</v>
+        <v>0.05045740410043708</v>
       </c>
       <c r="Y3">
-        <v>0.1673257260111296</v>
+        <v>0.1903235069624696</v>
       </c>
       <c r="Z3">
-        <v>0.7858355566335191</v>
+        <v>0.7896607091153168</v>
       </c>
       <c r="AA3">
-        <v>0.2162430870564842</v>
+        <v>0.242396591005472</v>
       </c>
       <c r="AB3">
-        <v>0.02431427658613419</v>
+        <v>0.05045745487499535</v>
       </c>
       <c r="AC3">
-        <v>0.19192881047035</v>
+        <v>0.1919391361304767</v>
       </c>
       <c r="AD3">
-        <v>0.301</v>
+        <v>0.201</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.301</v>
+        <v>0.201</v>
       </c>
       <c r="AG3">
-        <v>-8.109</v>
+        <v>-7.629</v>
       </c>
       <c r="AH3">
-        <v>0.003031188004149001</v>
+        <v>0.002022112453597047</v>
       </c>
       <c r="AI3">
-        <v>0.006445258131517526</v>
+        <v>0.00474045423456994</v>
       </c>
       <c r="AJ3">
-        <v>-0.08921675413407268</v>
+        <v>-0.08331240239813915</v>
       </c>
       <c r="AK3">
-        <v>-0.2117730014886005</v>
+        <v>-0.2206762893754881</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.003</v>
+        <v>-0.188</v>
       </c>
       <c r="AN3">
-        <v>0.02711711711711712</v>
+        <v>0.01970588235294118</v>
       </c>
       <c r="AP3">
-        <v>-0.7305405405405405</v>
+        <v>-0.7479411764705883</v>
       </c>
       <c r="AQ3">
-        <v>-4000</v>
+        <v>-59.04255319148936</v>
       </c>
     </row>
     <row r="4">
@@ -850,46 +850,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.04969999999999999</v>
+        <v>0.189</v>
       </c>
       <c r="E4">
-        <v>0.16</v>
+        <v>0.158</v>
       </c>
       <c r="G4">
-        <v>0.1345617336015052</v>
+        <v>0.1458305477559388</v>
       </c>
       <c r="H4">
-        <v>0.12619217543632</v>
+        <v>0.1397245621072336</v>
       </c>
       <c r="I4">
-        <v>0.1976845233236017</v>
+        <v>0.1017044237376799</v>
       </c>
       <c r="J4">
-        <v>0.155095280918352</v>
+        <v>0.1017044237376799</v>
       </c>
       <c r="K4">
-        <v>232.8</v>
+        <v>231.5</v>
       </c>
       <c r="L4">
-        <v>0.1510413287484591</v>
+        <v>0.1031777866916254</v>
       </c>
       <c r="M4">
-        <v>135</v>
+        <v>55.9958</v>
       </c>
       <c r="N4">
-        <v>0.1234567901234568</v>
+        <v>0.04444816637561518</v>
       </c>
       <c r="O4">
-        <v>0.5798969072164948</v>
+        <v>0.241882505399568</v>
       </c>
       <c r="P4">
-        <v>135</v>
+        <v>55.9958</v>
       </c>
       <c r="Q4">
-        <v>0.1234567901234568</v>
+        <v>0.04444816637561518</v>
       </c>
       <c r="R4">
-        <v>0.5798969072164948</v>
+        <v>0.241882505399568</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,55 +898,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2000.3</v>
+        <v>1172.8</v>
       </c>
       <c r="V4">
-        <v>1.829263831732967</v>
+        <v>0.9309414192729004</v>
       </c>
       <c r="W4">
-        <v>0.1763903621760873</v>
+        <v>0.1721189591078067</v>
       </c>
       <c r="X4">
-        <v>0.05383694837931793</v>
+        <v>0.08574250408419526</v>
       </c>
       <c r="Y4">
-        <v>0.1225534137967694</v>
+        <v>0.08637645502361144</v>
       </c>
       <c r="Z4">
-        <v>0.393110632637017</v>
+        <v>0.5438799489353785</v>
       </c>
       <c r="AA4">
-        <v>0.06096960400082921</v>
+        <v>0.05531499678895146</v>
       </c>
       <c r="AB4">
-        <v>0.02742189613910875</v>
+        <v>0.05055678470203379</v>
       </c>
       <c r="AC4">
-        <v>0.03354770786172046</v>
+        <v>0.004758212086917672</v>
       </c>
       <c r="AD4">
-        <v>4807.3</v>
+        <v>5233.8</v>
       </c>
       <c r="AE4">
-        <v>0.07922100666345055</v>
+        <v>0.05892229883763454</v>
       </c>
       <c r="AF4">
-        <v>4807.379221006664</v>
+        <v>5233.858922298838</v>
       </c>
       <c r="AG4">
-        <v>2807.079221006664</v>
+        <v>4061.058922298837</v>
       </c>
       <c r="AH4">
-        <v>0.814688632143626</v>
+        <v>0.8059953540716587</v>
       </c>
       <c r="AI4">
-        <v>0.7779838147892427</v>
+        <v>0.7999834595002402</v>
       </c>
       <c r="AJ4">
-        <v>0.7196570206519767</v>
+        <v>0.7632337150078558</v>
       </c>
       <c r="AK4">
-        <v>0.6717140891479411</v>
+        <v>0.7562973702918607</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>15.38793945078055</v>
+        <v>22.23307817132953</v>
       </c>
       <c r="AP4">
-        <v>8.985327540697437</v>
+        <v>17.25129742784312</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/chile/chile_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_financial_svcs_non_bank_insurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.12475</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E2">
-        <v>0.11085</v>
+        <v>0.04965</v>
       </c>
       <c r="G2">
-        <v>0.1493160927123191</v>
+        <v>0.1170690958272008</v>
       </c>
       <c r="H2">
-        <v>0.1432906715925584</v>
+        <v>0.1079995226540435</v>
       </c>
       <c r="I2">
-        <v>0.1052444102301238</v>
+        <v>0.1098229864603072</v>
       </c>
       <c r="J2">
-        <v>0.09627914565496511</v>
+        <v>0.09425202186312276</v>
       </c>
       <c r="K2">
-        <v>242.6</v>
+        <v>246.2</v>
       </c>
       <c r="L2">
-        <v>0.1066983331134275</v>
+        <v>0.09793547873821551</v>
       </c>
       <c r="M2">
-        <v>64.27579999999999</v>
+        <v>96.84</v>
       </c>
       <c r="N2">
-        <v>0.04729639440765268</v>
+        <v>0.07378285714285715</v>
       </c>
       <c r="O2">
-        <v>0.2649455894476504</v>
+        <v>0.3933387489845654</v>
       </c>
       <c r="P2">
-        <v>64.27579999999999</v>
+        <v>96.84</v>
       </c>
       <c r="Q2">
-        <v>0.04729639440765268</v>
+        <v>0.07378285714285715</v>
       </c>
       <c r="R2">
-        <v>0.2649455894476504</v>
+        <v>0.3933387489845654</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +636,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1180.63</v>
+        <v>1153.66</v>
       </c>
       <c r="V2">
-        <v>0.8687490802060338</v>
+        <v>0.8789790476190475</v>
       </c>
       <c r="W2">
-        <v>0.2064499350853567</v>
+        <v>0.1619952056057533</v>
       </c>
       <c r="X2">
-        <v>0.06809995409231617</v>
+        <v>0.07133909223322212</v>
       </c>
       <c r="Y2">
-        <v>0.1383499809930405</v>
+        <v>0.09065611337253117</v>
       </c>
       <c r="Z2">
-        <v>0.5461227238724513</v>
+        <v>0.4694897958091205</v>
       </c>
       <c r="AA2">
-        <v>0.1488557938972117</v>
+        <v>0.1005283028397791</v>
       </c>
       <c r="AB2">
-        <v>0.05050711978851457</v>
+        <v>0.05161911915230046</v>
       </c>
       <c r="AC2">
-        <v>0.09834867410869719</v>
+        <v>0.04890918368747867</v>
       </c>
       <c r="AD2">
-        <v>5234.001</v>
+        <v>4700.5</v>
       </c>
       <c r="AE2">
-        <v>0.05892229883763454</v>
+        <v>0.06497168716943753</v>
       </c>
       <c r="AF2">
-        <v>5234.059922298838</v>
+        <v>4700.564971687169</v>
       </c>
       <c r="AG2">
-        <v>4053.429922298837</v>
+        <v>3546.90497168717</v>
       </c>
       <c r="AH2">
-        <v>0.7938741622226679</v>
+        <v>0.7817252921463556</v>
       </c>
       <c r="AI2">
-        <v>0.7948627585188748</v>
+        <v>0.7496190547660085</v>
       </c>
       <c r="AJ2">
-        <v>0.7489112987124297</v>
+        <v>0.729905202870074</v>
       </c>
       <c r="AK2">
-        <v>0.750047644267252</v>
+        <v>0.6931684806681978</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.188</v>
+        <v>-0.29</v>
       </c>
       <c r="AN2">
-        <v>21.31055837398109</v>
+        <v>16.57749861574977</v>
       </c>
       <c r="AP2">
-        <v>16.50379030764248</v>
+        <v>12.50905483636635</v>
       </c>
       <c r="AQ2">
-        <v>-1272.872340425532</v>
+        <v>-952.0344827586208</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0605</v>
+        <v>-0.052</v>
       </c>
       <c r="E3">
-        <v>0.06370000000000001</v>
+        <v>-0.0617</v>
       </c>
       <c r="G3">
-        <v>0.41</v>
+        <v>0.745945945945946</v>
       </c>
       <c r="H3">
-        <v>0.41</v>
+        <v>0.745945945945946</v>
       </c>
       <c r="I3">
-        <v>0.37</v>
+        <v>0.3508108108108108</v>
       </c>
       <c r="J3">
-        <v>0.3069629629629629</v>
+        <v>0.2873930745666757</v>
       </c>
       <c r="K3">
-        <v>11.1</v>
+        <v>5.7</v>
       </c>
       <c r="L3">
-        <v>0.37</v>
+        <v>0.3081081081081081</v>
       </c>
       <c r="M3">
-        <v>8.279999999999999</v>
+        <v>1.54</v>
       </c>
       <c r="N3">
-        <v>0.08346774193548387</v>
+        <v>0.07738693467336684</v>
       </c>
       <c r="O3">
-        <v>0.7459459459459459</v>
+        <v>0.2701754385964912</v>
       </c>
       <c r="P3">
-        <v>8.279999999999999</v>
+        <v>1.54</v>
       </c>
       <c r="Q3">
-        <v>0.08346774193548387</v>
+        <v>0.07738693467336684</v>
       </c>
       <c r="R3">
-        <v>0.7459459459459459</v>
+        <v>0.2701754385964912</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,70 +767,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.83</v>
+        <v>1.56</v>
       </c>
       <c r="V3">
-        <v>0.07893145161290323</v>
+        <v>0.07839195979899498</v>
       </c>
       <c r="W3">
-        <v>0.2407809110629067</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="X3">
-        <v>0.05045740410043708</v>
+        <v>0.0527812996481594</v>
       </c>
       <c r="Y3">
-        <v>0.1903235069624696</v>
+        <v>0.08358233671547699</v>
       </c>
       <c r="Z3">
-        <v>0.7896607091153168</v>
+        <v>0.5413947499341547</v>
       </c>
       <c r="AA3">
-        <v>0.242396591005472</v>
+        <v>0.1555931017378333</v>
       </c>
       <c r="AB3">
-        <v>0.05045745487499535</v>
+        <v>0.0527812996481594</v>
       </c>
       <c r="AC3">
-        <v>0.1919391361304767</v>
+        <v>0.1028118020896739</v>
       </c>
       <c r="AD3">
-        <v>0.201</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.201</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-7.629</v>
+        <v>-1.56</v>
       </c>
       <c r="AH3">
-        <v>0.002022112453597047</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.00474045423456994</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.08331240239813915</v>
+        <v>-0.08505997818974918</v>
       </c>
       <c r="AK3">
-        <v>-0.2206762893754881</v>
+        <v>-0.2267441860465117</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.188</v>
+        <v>-0.29</v>
       </c>
       <c r="AN3">
-        <v>0.01970588235294118</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.7479411764705883</v>
+        <v>-0.2582781456953642</v>
       </c>
       <c r="AQ3">
-        <v>-59.04255319148936</v>
+        <v>-22.37931034482759</v>
       </c>
     </row>
     <row r="4">
@@ -850,46 +850,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.189</v>
+        <v>0.19</v>
       </c>
       <c r="E4">
-        <v>0.158</v>
+        <v>0.161</v>
       </c>
       <c r="G4">
-        <v>0.1458305477559388</v>
+        <v>0.1124068285645588</v>
       </c>
       <c r="H4">
-        <v>0.1397245621072336</v>
+        <v>0.103270016830969</v>
       </c>
       <c r="I4">
-        <v>0.1017044237376799</v>
+        <v>0.1080363892211934</v>
       </c>
       <c r="J4">
-        <v>0.1017044237376799</v>
+        <v>0.09693132718670953</v>
       </c>
       <c r="K4">
-        <v>231.5</v>
+        <v>240.5</v>
       </c>
       <c r="L4">
-        <v>0.1031777866916254</v>
+        <v>0.09637733429510299</v>
       </c>
       <c r="M4">
-        <v>55.9958</v>
+        <v>95.3</v>
       </c>
       <c r="N4">
-        <v>0.04444816637561518</v>
+        <v>0.07372737118984991</v>
       </c>
       <c r="O4">
-        <v>0.241882505399568</v>
+        <v>0.3962577962577962</v>
       </c>
       <c r="P4">
-        <v>55.9958</v>
+        <v>95.3</v>
       </c>
       <c r="Q4">
-        <v>0.04444816637561518</v>
+        <v>0.07372737118984991</v>
       </c>
       <c r="R4">
-        <v>0.241882505399568</v>
+        <v>0.3962577962577962</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,55 +898,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1172.8</v>
+        <v>1152.1</v>
       </c>
       <c r="V4">
-        <v>0.9309414192729004</v>
+        <v>0.8913043478260869</v>
       </c>
       <c r="W4">
-        <v>0.1721189591078067</v>
+        <v>0.1876267748478702</v>
       </c>
       <c r="X4">
-        <v>0.08574250408419526</v>
+        <v>0.08989688481828484</v>
       </c>
       <c r="Y4">
-        <v>0.08637645502361144</v>
+        <v>0.09772989002958535</v>
       </c>
       <c r="Z4">
-        <v>0.5438799489353785</v>
+        <v>0.4690279733212871</v>
       </c>
       <c r="AA4">
-        <v>0.05531499678895146</v>
+        <v>0.04546350394172495</v>
       </c>
       <c r="AB4">
-        <v>0.05055678470203379</v>
+        <v>0.05045693865644151</v>
       </c>
       <c r="AC4">
-        <v>0.004758212086917672</v>
+        <v>-0.004993434714716562</v>
       </c>
       <c r="AD4">
-        <v>5233.8</v>
+        <v>4700.5</v>
       </c>
       <c r="AE4">
-        <v>0.05892229883763454</v>
+        <v>0.06497168716943753</v>
       </c>
       <c r="AF4">
-        <v>5233.858922298838</v>
+        <v>4700.564971687169</v>
       </c>
       <c r="AG4">
-        <v>4061.058922298837</v>
+        <v>3548.46497168717</v>
       </c>
       <c r="AH4">
-        <v>0.8059953540716587</v>
+        <v>0.7843209712887125</v>
       </c>
       <c r="AI4">
-        <v>0.7999834595002402</v>
+        <v>0.7506293738570625</v>
       </c>
       <c r="AJ4">
-        <v>0.7632337150078558</v>
+        <v>0.7329926353891687</v>
       </c>
       <c r="AK4">
-        <v>0.7562973702918607</v>
+        <v>0.6944070166128606</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>22.23307817132953</v>
+        <v>16.93831146601707</v>
       </c>
       <c r="AP4">
-        <v>17.25129742784312</v>
+        <v>12.78693860582677</v>
       </c>
     </row>
   </sheetData>
